--- a/KAMCHATKA_ZAPOLNENIE/00_СВОДКА_кому_что_отправить.xlsx
+++ b/KAMCHATKA_ZAPOLNENIE/00_СВОДКА_кому_что_отправить.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Камчатскэнерго 32616346943 — предполагаемые поставщики: каждой из 315 позиций назначен один поставщик; файл для заполнения — в папке KAMCHATKA_ZAPOLNENIE</t>
+          <t>Камчатскэнерго 32616346943 — предполагаемые поставщики: каждой из 315 позиций назначен основной поставщик + по позициям ДН.РУ параллельный запрос российскому заводу с записью ПП 719 (основание «альтернатива ДН.РУ»); файлы — в папке KAMCHATKA_ZAPOLNENIE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -624,38 +624,38 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>ООО «Торговый Дом АДЛ»</t>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68</t>
+          <t>+7 (342) 270-07-34</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>info@adl.ru</t>
+          <t>sales@ptza.ru</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>106</v>
+        <v>300</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>1.3/154, 1.3/155, 1.3/156, 1.3/157, 1.3/158, 1.3/159, 1.3/160, 1.3/161, 1.3/162, 1.6/11, 1.6/89, 1.6/90, 1.6/91</t>
+          <t>1.1/2, 1.1/3, 1.1/4, 1.1/5, 1.1/7, 1.1/8, 1.1/9, 1.1/10, 1.1/11, 1.1/12, 1.1/13, 1.3/23, 1.3/24, 1.3/54, 1.3/55, 1.3/56, 1.3/57, 1.3/58, 1.3/59, 1.3/60, 1.3/61, 1.3/62, 1.3/63, 1.3/68, 1.3/69, 1.3/70, 1.3/71, 1.3/72, 1.3/73, 1.3/74, 1.3/75, 1.3/76, 1.3/77, 1.3/78, 1.3/79, 1.3/80, 1.3/81, 1.3/82, 1.3/83, 1.3/84, 1.3/85, 1.3/86, 1.3/87, 1.3/88, 1.3/89, 1.3/90, 1.3/91, 1.3/92, 1.5/2, 1.5/3, 1.6/15, 1</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>КП получено — подтвердить и дополнить ре — 12; у ДН.РУ — 1</t>
+          <t>альтернатива ДН.РУ — 69; новый запрос КП — 4</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>03_ООО_Торговый_Дом_АДЛ.xlsx</t>
+          <t>03_ООО_Пермский_трубопроводный_завод.xlsx</t>
         </is>
       </c>
     </row>
@@ -665,38 +665,38 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>ООО «Сибирский завод трубопроводной арматуры» (СИБЗТА)</t>
+          <t>ООО «Торговый Дом АДЛ»</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>8-800-350-91-13</t>
+          <t>+7 (495) 937-89-68</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>sales@sibzta.ru</t>
+          <t>info@adl.ru</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>1.1/11, 1.3/78, 1.3/79, 1.3/80, 1.3/81, 1.3/82, 1.3/83, 1.3/84, 1.5/2, 1.5/3</t>
+          <t>1.3/16, 1.3/17, 1.3/18, 1.3/22, 1.3/30, 1.3/31, 1.3/36, 1.3/37, 1.3/38, 1.3/154, 1.3/155, 1.3/156, 1.3/157, 1.3/158, 1.3/159, 1.3/160, 1.3/161, 1.3/162, 1.6/4, 1.6/5, 1.6/6, 1.6/11, 1.6/89, 1.6/90, 1.6/91</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>у ДН.РУ — 10</t>
+          <t>альтернатива ДН.РУ — 12; КП получено — подтвердить и дополнить ре — 12; у ДН.РУ — 1</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>04_ООО_Сибирский_завод_трубопроводной_армат.xlsx</t>
+          <t>04_ООО_Торговый_Дом_АДЛ.xlsx</t>
         </is>
       </c>
     </row>
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>1.1/2, 1.1/4, 1.3/41, 1.3/42, 1.3/43, 1.3/44, 1.3/63, 1.3/67, 1.6/20</t>
+          <t>1.1/1, 1.1/2, 1.1/4, 1.3/14, 1.3/15, 1.3/21, 1.3/26, 1.3/27, 1.3/28, 1.3/29, 1.3/41, 1.3/42, 1.3/43, 1.3/44, 1.3/63, 1.3/67, 1.6/12, 1.6/13, 1.6/14, 1.6/20</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>у ДН.РУ — 9</t>
+          <t>альтернатива ДН.РУ — 11; у ДН.РУ — 9</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -747,38 +747,38 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>ООО «Ридан»</t>
+          <t>АО «Энерготехномаш»</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 792-57-57</t>
+          <t>+7 (3012) 55-32-29</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>call@ridan.ru</t>
+          <t>osb@etmu.ru</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>1.3/19, 1.3/27, 1.3/32, 1.3/33, 1.3/34, 1.3/35, 1.7/1</t>
+          <t>1.3/1, 1.3/6, 1.3/7, 1.3/8, 1.3/9, 1.3/10, 1.3/11, 1.3/12, 1.3/13, 1.3/67, 1.6/1, 1.6/2, 1.6/3, 1.7/1</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>у ДН.РУ — 4; проверенного поставщика нет — Ридан (ори — 3</t>
+          <t>альтернатива ДН.РУ — 14</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>06_ООО_Ридан.xlsx</t>
+          <t>06_АО_Энерготехномаш.xlsx</t>
         </is>
       </c>
     </row>
@@ -788,38 +788,38 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
+          <t>ООО «Сибирский завод трубопроводной арматуры» (СИБЗТА)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+7 (4725) 469-470 (завод)</t>
+          <t>8-800-350-91-13</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>zavod@saz-avangard.ru</t>
+          <t>sales@sibzta.ru</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>1.3/2, 1.3/3, 1.3/4, 1.3/5, 1.3/163</t>
+          <t>1.1/11, 1.3/78, 1.3/79, 1.3/80, 1.3/81, 1.3/82, 1.3/83, 1.3/84, 1.5/2, 1.5/3</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>новый запрос КП — 5</t>
+          <t>у ДН.РУ — 10</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>07_ООО_Арма-Пром.xlsx</t>
+          <t>07_ООО_Сибирский_завод_трубопроводной_армат.xlsx</t>
         </is>
       </c>
     </row>
@@ -829,38 +829,38 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>ООО «Пензапромарматура» (КИПИКА), Хрипунова Светлана</t>
+          <t>ОАО «Литейно-механический завод» (ОАО «ЛМЗ»)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+7 (8412) 909-200</t>
+          <t>+7 (83162) 5-70-90</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>b18bk@11b18bk.ru</t>
+          <t>marketlmz@mail.ru</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>172</v>
+        <v>96</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>1.3/39, 1.3/100, 1.6/16, 1.6/50</t>
+          <t>1.3/93, 1.3/94, 1.3/95, 1.3/96, 1.3/97, 1.3/98, 1.3/99, 1.6/47, 1.6/48, 1.6/49</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>КП получено — подтвердить и дополнить ре — 4</t>
+          <t>альтернатива ДН.РУ — 10</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>08_ООО_Пензапромарматура.xlsx</t>
+          <t>08_ОАО_Литейно-механический_завод.xlsx</t>
         </is>
       </c>
     </row>
@@ -870,38 +870,34 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>ООО «БК-Арматура» (дистрибьютор)</t>
+          <t>ООО «Бологовский арматурный завод» (ТМ «БАЗ», латунная арматура)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>8 (495) 925-51-64</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>info@bkarm.ru</t>
-        </is>
-      </c>
+          <t>контакт не проверен</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>39</v>
+        <v>126</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>1.3/93, 1.3/95, 1.6/47, 1.6/49</t>
+          <t>1.3/48, 1.3/49, 1.3/50, 1.3/51, 1.3/52, 1.3/53, 1.6/17, 1.6/18, 1.6/19</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>у ДН.РУ — 4</t>
+          <t>альтернатива ДН.РУ — 9</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>09_ООО_БК-Арматура.xlsx</t>
+          <t>09_ООО_Бологовский_арматурный_завод.xlsx</t>
         </is>
       </c>
     </row>
@@ -911,38 +907,38 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+          <t>ООО «Ридан»</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+7 (342) 270-07-34</t>
+          <t>+7 (495) 792-57-57</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>sales@ptza.ru</t>
+          <t>call@ridan.ru</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>1.3/23, 1.3/24, 1.3/56, 1.3/57</t>
+          <t>1.3/19, 1.3/27, 1.3/32, 1.3/33, 1.3/34, 1.3/35, 1.7/1</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>новый запрос КП — 4</t>
+          <t>у ДН.РУ — 4; проверенного поставщика нет — Ридан (ори — 3</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>10_ООО_Пермский_трубопроводный_завод.xlsx</t>
+          <t>10_ООО_Ридан.xlsx</t>
         </is>
       </c>
     </row>
@@ -952,38 +948,38 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>ООО «Лидер-Энерго» / «Транс-Энерго»</t>
+          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>+7 (8482) 21-66-32</t>
+          <t>+7 (4725) 469-470 (завод)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>trans-energo@bk.ru</t>
+          <t>zavod@saz-avangard.ru</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>1.3/151, 1.3/152, 1.3/153</t>
+          <t>1.3/2, 1.3/3, 1.3/4, 1.3/5, 1.3/163</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>КП получено — подтвердить и дополнить ре — 3</t>
+          <t>новый запрос КП — 5</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>11_ООО_Лидер-Энерго_Транс-Энерго.xlsx</t>
+          <t>11_ООО_Арма-Пром.xlsx</t>
         </is>
       </c>
     </row>
@@ -993,38 +989,38 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>ООО «ПромАрм» (PromArm®)</t>
+          <t>АО «Энергия» (производитель арматуры ДЕНДОР/DENDOR)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>+7 (8412) 35-07-97</t>
+          <t>8-800-333-40-30</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>info@promarm.ru</t>
+          <t>zakaz@dendor.ru</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>1.1/22, 1.1/23, 1.3/150</t>
+          <t>1.3/19, 1.3/20, 1.6/7, 1.6/8, 1.6/9</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>новый запрос КП — 3</t>
+          <t>альтернатива ДН.РУ — 5</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>12_ООО_ПромАрм.xlsx</t>
+          <t>12_АО_Энергия.xlsx</t>
         </is>
       </c>
     </row>
@@ -1034,38 +1030,38 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>ООО «Нижегородский завод «Старт»</t>
+          <t>ООО «Пензапромарматура» (КИПИКА), Хрипунова Светлана</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>+7 (831) 253-83-11</t>
+          <t>+7 (8412) 909-200</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>start.nn@mail.ru</t>
+          <t>b18bk@11b18bk.ru</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5</v>
+        <v>172</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>1.3/45, 1.3/46, 1.3/47</t>
+          <t>1.3/39, 1.3/100, 1.6/16, 1.6/50</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>новый запрос КП — 3</t>
+          <t>КП получено — подтвердить и дополнить ре — 4</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>13_ООО_Нижегородский_завод_Старт.xlsx</t>
+          <t>13_ООО_Пензапромарматура.xlsx</t>
         </is>
       </c>
     </row>
@@ -1075,34 +1071,38 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>АО «Тулаэлектропривод»</t>
+          <t>ООО «БК-Арматура» (дистрибьютор)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>по КП 10/160</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr"/>
+          <t>8 (495) 925-51-64</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>info@bkarm.ru</t>
+        </is>
+      </c>
       <c r="E16" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>1.1/24</t>
+          <t>1.3/93, 1.3/95, 1.6/47, 1.6/49</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>торг — 1</t>
+          <t>у ДН.РУ — 4</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>14_АО_Тулаэлектропривод.xlsx</t>
+          <t>14_ООО_БК-Арматура.xlsx</t>
         </is>
       </c>
     </row>
@@ -1112,38 +1112,38 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>ООО «ТЕМПЕР» (завод TEMPER)</t>
+          <t>ООО «Лидер-Энерго» / «Транс-Энерго»</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>+7 (3522) 22-88-88</t>
+          <t>+7 (8482) 21-66-32</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>temper@temper.ru</t>
+          <t>trans-energo@bk.ru</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>1.3/148</t>
+          <t>1.3/151, 1.3/152, 1.3/153</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>новый запрос КП — 1</t>
+          <t>КП получено — подтвердить и дополнить ре — 3</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>15_ООО_ТЕМПЕР.xlsx</t>
+          <t>15_ООО_Лидер-Энерго_Транс-Энерго.xlsx</t>
         </is>
       </c>
     </row>
@@ -1153,38 +1153,38 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>ООО «Челябинский завод трубопроводной арматуры» (ООО «ЧЗТА», бренд «ЧЗТА АРМАКОМ»)</t>
+          <t>ООО «ПромАрм» (PromArm®)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>+7 (351) 215-53-33</t>
+          <t>+7 (8412) 35-07-97</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>zakaz@chzta.ru</t>
+          <t>info@promarm.ru</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>1.1/6</t>
+          <t>1.1/22, 1.1/23, 1.3/150</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>новый запрос КП — 1</t>
+          <t>новый запрос КП — 3</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>16_ООО_Челябинский_завод_трубопроводной_арм.xlsx</t>
+          <t>16_ООО_ПромАрм.xlsx</t>
         </is>
       </c>
     </row>
@@ -1194,38 +1194,38 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>АО «АБС ЗЭиМ Автоматизация»</t>
+          <t>ООО «Нижегородский завод «Старт»</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>+7 (8352) 30-51-48</t>
+          <t>+7 (831) 253-83-11</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>sales@zeim.ru</t>
+          <t>start.nn@mail.ru</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>1.6/93</t>
+          <t>1.3/45, 1.3/46, 1.3/47</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>новый запрос КП — 1</t>
+          <t>новый запрос КП — 3</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>17_АО_АБС_ЗЭиМ_Автоматизация.xlsx</t>
+          <t>17_ООО_Нижегородский_завод_Старт.xlsx</t>
         </is>
       </c>
     </row>
@@ -1235,38 +1235,34 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>ЗАО «Арматурная Компания «ФОБОС»</t>
+          <t>АО «Тулаэлектропривод»</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>8-800-700-62-60</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>info@fobosarm.ru</t>
-        </is>
-      </c>
+          <t>по КП 10/160</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>1.3/135</t>
+          <t>1.1/24</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>новый запрос КП — 1</t>
+          <t>торг — 1</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>18_ЗАО_Арматурная_Компания_ФОБОС.xlsx</t>
+          <t>18_АО_Тулаэлектропривод.xlsx</t>
         </is>
       </c>
     </row>
@@ -1276,28 +1272,28 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>ООО «ПКФ «ТЕРМ»</t>
+          <t>ООО «ТЕМПЕР» (завод TEMPER)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+7 (927) 279-09-83</t>
+          <t>+7 (3522) 22-88-88</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>term1998@yandex.ru</t>
+          <t>temper@temper.ru</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>1.4/1</t>
+          <t>1.3/148</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1307,7 +1303,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>19_ООО_ПКФ_ТЕРМ.xlsx</t>
+          <t>19_ООО_ТЕМПЕР.xlsx</t>
         </is>
       </c>
     </row>
@@ -1317,28 +1313,28 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Компания «Арматон»</t>
+          <t>ООО «Челябинский завод трубопроводной арматуры» (ООО «ЧЗТА», бренд «ЧЗТА АРМАКОМ»)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+7 (963) 728-59-82</t>
+          <t>+7 (351) 215-53-33</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>armaton@bk.ru</t>
+          <t>zakaz@chzta.ru</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>1.3/40</t>
+          <t>1.1/6</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1348,7 +1344,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>20_Компания_Арматон.xlsx</t>
+          <t>20_ООО_Челябинский_завод_трубопроводной_арм.xlsx</t>
         </is>
       </c>
     </row>
@@ -1358,59 +1354,260 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>ТЕД Газовые системы (TEDGAS; сервисный центр DUNGS; домен dungs.ru ведёт на tedgas.ru)</t>
+          <t>АО «АБС ЗЭиМ Автоматизация»</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>8-800-550-60-80</t>
+          <t>+7 (8352) 30-51-48</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>info@tedgas.ru (отдел продаж: retail@karldungs.ru)</t>
+          <t>sales@zeim.ru</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>1.6/93</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>новый запрос КП — 1</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>21_АО_АБС_ЗЭиМ_Автоматизация.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>ЗАО «Арматурная Компания «ФОБОС»</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>8-800-700-62-60</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>info@fobosarm.ru</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>1.3/135</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>новый запрос КП — 1</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>22_ЗАО_Арматурная_Компания_ФОБОС.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>ООО «ПКФ «ТЕРМ»</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+7 (927) 279-09-83</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>term1998@yandex.ru</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>1.4/1</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>новый запрос КП — 1</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>23_ООО_ПКФ_ТЕРМ.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Компания «Арматон»</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+7 (963) 728-59-82</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>armaton@bk.ru</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>1.3/40</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>новый запрос КП — 1</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>24_Компания_Арматон.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>ТЕД Газовые системы (TEDGAS; сервисный центр DUNGS; домен dungs.ru ведёт на tedgas.ru)</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>8-800-550-60-80</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>info@tedgas.ru (отдел продаж: retail@karldungs.ru)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>1.6/92</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>новый запрос КП — 1</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>21_ТЕД_Газовые_системы.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="6" t="inlineStr"/>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>25_ТЕД_Газовые_системы.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>ООО ПКФ «Экс-Форма»</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>контакт не проверен</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>1.6/10</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>альтернатива ДН.РУ — 1</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>26_ООО_ПКФ_Экс-Форма.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="6" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr"/>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="7" t="n">
-        <v>315</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>3383</v>
-      </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="n"/>
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="7" t="n">
+        <v>446</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>3996</v>
+      </c>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
